--- a/diseases/d035/2005-2009.xlsx
+++ b/diseases/d035/2005-2009.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -1653,9 +1650,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2239,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2680,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3121,6 @@
       <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -3725,9 +3710,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4317,9 +4299,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4909,9 +4888,6 @@
       <c r="O30" t="n">
         <v>4</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.008359169436268481</v>
       </c>
@@ -5501,9 +5477,6 @@
       <c r="O34" t="n">
         <v>16</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.03343667774507392</v>
       </c>
@@ -6093,9 +6066,6 @@
       <c r="O38" t="n">
         <v>21</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.04388563954040952</v>
       </c>
@@ -6685,9 +6655,6 @@
       <c r="O42" t="n">
         <v>36</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.07523252492641631</v>
       </c>
@@ -7277,9 +7244,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.00626937707720136</v>
       </c>
@@ -7869,9 +7833,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -8461,9 +8422,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9053,9 +9011,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -9645,9 +9600,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10237,9 +10189,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -10829,9 +10778,6 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -11421,9 +11367,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -12013,9 +11956,6 @@
       <c r="O78" t="n">
         <v>7</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01458135345893399</v>
       </c>
@@ -12605,9 +12545,6 @@
       <c r="O82" t="n">
         <v>12</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.02499660592960112</v>
       </c>
@@ -13197,9 +13134,6 @@
       <c r="O86" t="n">
         <v>36</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.07498981778880337</v>
       </c>
@@ -13789,9 +13723,6 @@
       <c r="O90" t="n">
         <v>46</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.09582032273013764</v>
       </c>
@@ -14381,9 +14312,6 @@
       <c r="O94" t="n">
         <v>11</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.02291355543546769</v>
       </c>
@@ -14973,9 +14901,6 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -15417,9 +15342,6 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -16009,9 +15931,6 @@
       <c r="O105" t="n">
         <v>3</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.006226893231623397</v>
       </c>
@@ -16601,9 +16520,6 @@
       <c r="O109" t="n">
         <v>3</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.006226893231623397</v>
       </c>
@@ -17193,9 +17109,6 @@
       <c r="O113" t="n">
         <v>2</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -17785,9 +17698,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18377,9 +18287,6 @@
       <c r="O121" t="n">
         <v>2</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -18969,9 +18876,6 @@
       <c r="O125" t="n">
         <v>5</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.010378155386039</v>
       </c>
@@ -19561,9 +19465,6 @@
       <c r="O129" t="n">
         <v>23</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.04773951477577938</v>
       </c>
@@ -20153,9 +20054,6 @@
       <c r="O133" t="n">
         <v>63</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.1307647578640914</v>
       </c>
@@ -20745,9 +20643,6 @@
       <c r="O137" t="n">
         <v>83</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.1722773794082473</v>
       </c>
@@ -21337,9 +21232,6 @@
       <c r="O141" t="n">
         <v>20</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.04151262154415598</v>
       </c>
@@ -21929,9 +21821,6 @@
       <c r="O145" t="n">
         <v>4</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -22521,9 +22410,6 @@
       <c r="O149" t="n">
         <v>4</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -23113,9 +22999,6 @@
       <c r="O153" t="n">
         <v>2</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -23705,9 +23588,6 @@
       <c r="O157" t="n">
         <v>2</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -24297,9 +24177,6 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -24889,9 +24766,6 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -25629,9 +25503,6 @@
       <c r="O170" t="n">
         <v>2</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -26369,9 +26240,6 @@
       <c r="O175" t="n">
         <v>5</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01033987307557643</v>
       </c>
@@ -27109,9 +26977,6 @@
       <c r="O180" t="n">
         <v>15</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.03101961922672929</v>
       </c>
@@ -27849,9 +27714,6 @@
       <c r="O185" t="n">
         <v>39</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.08065100998949613</v>
       </c>
@@ -28589,9 +28451,6 @@
       <c r="O190" t="n">
         <v>23</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.04756341614765157</v>
       </c>
@@ -29329,9 +29188,6 @@
       <c r="O195" t="n">
         <v>2</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -30069,9 +29925,6 @@
       <c r="O200" t="n">
         <v>3</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -30809,9 +30662,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -31401,9 +31251,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -31993,9 +31840,6 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -32733,9 +32577,6 @@
       <c r="O218" t="n">
         <v>1</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -33473,9 +33314,6 @@
       <c r="O223" t="n">
         <v>2</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -34213,9 +34051,6 @@
       <c r="O228" t="n">
         <v>2</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -34953,9 +34788,6 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -35693,9 +35525,6 @@
       <c r="O238" t="n">
         <v>7</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.01441910973676854</v>
       </c>
@@ -36433,9 +36262,6 @@
       <c r="O243" t="n">
         <v>17</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.03501783793215218</v>
       </c>
@@ -37173,9 +36999,6 @@
       <c r="O248" t="n">
         <v>22</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.045317202029844</v>
       </c>
@@ -37912,9 +37735,6 @@
       </c>
       <c r="O253" t="n">
         <v>6</v>
-      </c>
-      <c r="Q253" t="n">
-        <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>0.01235923691723018</v>
